--- a/sample-project2/srcs/CSharp_ASPNET/build/test-results/independent-browser/seed-career.xlsx
+++ b/sample-project2/srcs/CSharp_ASPNET/build/test-results/independent-browser/seed-career.xlsx
@@ -26,7 +26,7 @@
     <x:t>2026年10月29日現在</x:t>
   </x:si>
   <x:si>
-    <x:t>作成日時（JST）：2026年10月29日 01:05</x:t>
+    <x:t>作成日時（JST）：2026年10月29日 14:12</x:t>
   </x:si>
   <x:si>
     <x:t>氏名</x:t>
@@ -177,7 +177,7 @@
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="10.5"/>
-      <x:color rgb="FF000000"/>
+      <x:color rgb="FF202B38"/>
       <x:name val="Meiryo"/>
       <x:family val="2"/>
     </x:font>
@@ -185,7 +185,7 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="18"/>
-      <x:color rgb="FF000000"/>
+      <x:color rgb="FF173650"/>
       <x:name val="Meiryo"/>
       <x:family val="2"/>
     </x:font>
@@ -193,20 +193,25 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
-      <x:color rgb="FF000000"/>
+      <x:color rgb="FF173650"/>
       <x:name val="Meiryo"/>
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="2">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="1">
+  <x:borders count="8">
     <x:border diagonalUp="0" diagonalDown="0">
       <x:left style="none">
         <x:color rgb="FF000000"/>
@@ -219,54 +224,215 @@
       </x:top>
       <x:bottom style="none">
         <x:color rgb="FF000000"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FFAEB8C5"/>
+      </x:left>
+      <x:right style="none">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFAEB8C5"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFAEB8C5"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="none">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFAEB8C5"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFAEB8C5"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFAEB8C5"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFAEB8C5"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFAEB8C5"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="none">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="none">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="FF173650"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FFAEB8C5"/>
+      </x:left>
+      <x:right style="none">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFAEB8C5"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="FF173650"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="none">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFAEB8C5"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="FF173650"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFAEB8C5"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFAEB8C5"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="FF173650"/>
       </x:bottom>
       <x:diagonal style="none">
         <x:color rgb="FF000000"/>
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="6">
+  <x:cellStyleXfs count="12">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="2" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="2" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="3" fillId="2" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="3" fillId="2" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="6" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="7" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="6">
+  <x:cellXfs count="12">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -590,49 +756,93 @@
       </x:c>
     </x:row>
     <x:row r="5" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A5" s="3" t="s">
+      <x:c r="A5" s="4" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G5" s="3" t="s">
+      <x:c r="B5" s="5"/>
+      <x:c r="C5" s="5"/>
+      <x:c r="D5" s="5"/>
+      <x:c r="E5" s="5"/>
+      <x:c r="F5" s="6"/>
+      <x:c r="G5" s="4" t="s">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="H5" s="5"/>
+      <x:c r="I5" s="5"/>
+      <x:c r="J5" s="5"/>
+      <x:c r="K5" s="5"/>
+      <x:c r="L5" s="5"/>
+      <x:c r="M5" s="5"/>
+      <x:c r="N5" s="5"/>
+      <x:c r="O5" s="5"/>
+      <x:c r="P5" s="5"/>
+      <x:c r="Q5" s="5"/>
+      <x:c r="R5" s="5"/>
+      <x:c r="S5" s="5"/>
+      <x:c r="T5" s="5"/>
+      <x:c r="U5" s="5"/>
+      <x:c r="V5" s="5"/>
+      <x:c r="W5" s="5"/>
+      <x:c r="X5" s="6"/>
     </x:row>
     <x:row r="6" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A6" s="3" t="s">
+      <x:c r="A6" s="4" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G6" s="3" t="s">
+      <x:c r="B6" s="5"/>
+      <x:c r="C6" s="5"/>
+      <x:c r="D6" s="5"/>
+      <x:c r="E6" s="5"/>
+      <x:c r="F6" s="6"/>
+      <x:c r="G6" s="4" t="s">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="H6" s="5"/>
+      <x:c r="I6" s="5"/>
+      <x:c r="J6" s="5"/>
+      <x:c r="K6" s="5"/>
+      <x:c r="L6" s="5"/>
+      <x:c r="M6" s="5"/>
+      <x:c r="N6" s="5"/>
+      <x:c r="O6" s="5"/>
+      <x:c r="P6" s="5"/>
+      <x:c r="Q6" s="5"/>
+      <x:c r="R6" s="5"/>
+      <x:c r="S6" s="5"/>
+      <x:c r="T6" s="5"/>
+      <x:c r="U6" s="5"/>
+      <x:c r="V6" s="5"/>
+      <x:c r="W6" s="5"/>
+      <x:c r="X6" s="6"/>
     </x:row>
     <x:row r="7" spans="1:24" ht="15" customHeight="1"/>
     <x:row r="8" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A8" s="4" t="s">
+      <x:c r="A8" s="7" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B8" s="5"/>
-      <x:c r="C8" s="5"/>
-      <x:c r="D8" s="5"/>
-      <x:c r="E8" s="5"/>
-      <x:c r="F8" s="5"/>
-      <x:c r="G8" s="5"/>
-      <x:c r="H8" s="5"/>
-      <x:c r="I8" s="5"/>
-      <x:c r="J8" s="5"/>
-      <x:c r="K8" s="5"/>
-      <x:c r="L8" s="5"/>
-      <x:c r="M8" s="5"/>
-      <x:c r="N8" s="5"/>
-      <x:c r="O8" s="5"/>
-      <x:c r="P8" s="5"/>
-      <x:c r="Q8" s="5"/>
-      <x:c r="R8" s="5"/>
-      <x:c r="S8" s="5"/>
-      <x:c r="T8" s="5"/>
-      <x:c r="U8" s="5"/>
-      <x:c r="V8" s="5"/>
-      <x:c r="W8" s="5"/>
-      <x:c r="X8" s="5"/>
+      <x:c r="B8" s="8"/>
+      <x:c r="C8" s="8"/>
+      <x:c r="D8" s="8"/>
+      <x:c r="E8" s="8"/>
+      <x:c r="F8" s="8"/>
+      <x:c r="G8" s="8"/>
+      <x:c r="H8" s="8"/>
+      <x:c r="I8" s="8"/>
+      <x:c r="J8" s="8"/>
+      <x:c r="K8" s="8"/>
+      <x:c r="L8" s="8"/>
+      <x:c r="M8" s="8"/>
+      <x:c r="N8" s="8"/>
+      <x:c r="O8" s="8"/>
+      <x:c r="P8" s="8"/>
+      <x:c r="Q8" s="8"/>
+      <x:c r="R8" s="8"/>
+      <x:c r="S8" s="8"/>
+      <x:c r="T8" s="8"/>
+      <x:c r="U8" s="8"/>
+      <x:c r="V8" s="8"/>
+      <x:c r="W8" s="8"/>
+      <x:c r="X8" s="8"/>
     </x:row>
     <x:row r="9" spans="1:24" ht="15" customHeight="1">
       <x:c r="A9" s="3" t="s">
@@ -641,32 +851,32 @@
     </x:row>
     <x:row r="10" spans="1:24" ht="15" customHeight="1"/>
     <x:row r="11" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A11" s="4" t="s">
+      <x:c r="A11" s="7" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B11" s="5"/>
-      <x:c r="C11" s="5"/>
-      <x:c r="D11" s="5"/>
-      <x:c r="E11" s="5"/>
-      <x:c r="F11" s="5"/>
-      <x:c r="G11" s="5"/>
-      <x:c r="H11" s="5"/>
-      <x:c r="I11" s="5"/>
-      <x:c r="J11" s="5"/>
-      <x:c r="K11" s="5"/>
-      <x:c r="L11" s="5"/>
-      <x:c r="M11" s="5"/>
-      <x:c r="N11" s="5"/>
-      <x:c r="O11" s="5"/>
-      <x:c r="P11" s="5"/>
-      <x:c r="Q11" s="5"/>
-      <x:c r="R11" s="5"/>
-      <x:c r="S11" s="5"/>
-      <x:c r="T11" s="5"/>
-      <x:c r="U11" s="5"/>
-      <x:c r="V11" s="5"/>
-      <x:c r="W11" s="5"/>
-      <x:c r="X11" s="5"/>
+      <x:c r="B11" s="8"/>
+      <x:c r="C11" s="8"/>
+      <x:c r="D11" s="8"/>
+      <x:c r="E11" s="8"/>
+      <x:c r="F11" s="8"/>
+      <x:c r="G11" s="8"/>
+      <x:c r="H11" s="8"/>
+      <x:c r="I11" s="8"/>
+      <x:c r="J11" s="8"/>
+      <x:c r="K11" s="8"/>
+      <x:c r="L11" s="8"/>
+      <x:c r="M11" s="8"/>
+      <x:c r="N11" s="8"/>
+      <x:c r="O11" s="8"/>
+      <x:c r="P11" s="8"/>
+      <x:c r="Q11" s="8"/>
+      <x:c r="R11" s="8"/>
+      <x:c r="S11" s="8"/>
+      <x:c r="T11" s="8"/>
+      <x:c r="U11" s="8"/>
+      <x:c r="V11" s="8"/>
+      <x:c r="W11" s="8"/>
+      <x:c r="X11" s="8"/>
     </x:row>
     <x:row r="12" spans="1:24" ht="15" customHeight="1">
       <x:c r="A12" s="3" t="s">
@@ -675,32 +885,32 @@
     </x:row>
     <x:row r="13" spans="1:24" ht="15" customHeight="1"/>
     <x:row r="14" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A14" s="4" t="s">
+      <x:c r="A14" s="7" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B14" s="5"/>
-      <x:c r="C14" s="5"/>
-      <x:c r="D14" s="5"/>
-      <x:c r="E14" s="5"/>
-      <x:c r="F14" s="5"/>
-      <x:c r="G14" s="5"/>
-      <x:c r="H14" s="5"/>
-      <x:c r="I14" s="5"/>
-      <x:c r="J14" s="5"/>
-      <x:c r="K14" s="5"/>
-      <x:c r="L14" s="5"/>
-      <x:c r="M14" s="5"/>
-      <x:c r="N14" s="5"/>
-      <x:c r="O14" s="5"/>
-      <x:c r="P14" s="5"/>
-      <x:c r="Q14" s="5"/>
-      <x:c r="R14" s="5"/>
-      <x:c r="S14" s="5"/>
-      <x:c r="T14" s="5"/>
-      <x:c r="U14" s="5"/>
-      <x:c r="V14" s="5"/>
-      <x:c r="W14" s="5"/>
-      <x:c r="X14" s="5"/>
+      <x:c r="B14" s="8"/>
+      <x:c r="C14" s="8"/>
+      <x:c r="D14" s="8"/>
+      <x:c r="E14" s="8"/>
+      <x:c r="F14" s="8"/>
+      <x:c r="G14" s="8"/>
+      <x:c r="H14" s="8"/>
+      <x:c r="I14" s="8"/>
+      <x:c r="J14" s="8"/>
+      <x:c r="K14" s="8"/>
+      <x:c r="L14" s="8"/>
+      <x:c r="M14" s="8"/>
+      <x:c r="N14" s="8"/>
+      <x:c r="O14" s="8"/>
+      <x:c r="P14" s="8"/>
+      <x:c r="Q14" s="8"/>
+      <x:c r="R14" s="8"/>
+      <x:c r="S14" s="8"/>
+      <x:c r="T14" s="8"/>
+      <x:c r="U14" s="8"/>
+      <x:c r="V14" s="8"/>
+      <x:c r="W14" s="8"/>
+      <x:c r="X14" s="8"/>
     </x:row>
     <x:row r="15" spans="1:24" ht="15" customHeight="1">
       <x:c r="A15" s="3" t="s">
@@ -709,32 +919,32 @@
     </x:row>
     <x:row r="16" spans="1:24" ht="15" customHeight="1"/>
     <x:row r="17" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A17" s="4" t="s">
+      <x:c r="A17" s="7" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B17" s="5"/>
-      <x:c r="C17" s="5"/>
-      <x:c r="D17" s="5"/>
-      <x:c r="E17" s="5"/>
-      <x:c r="F17" s="5"/>
-      <x:c r="G17" s="5"/>
-      <x:c r="H17" s="5"/>
-      <x:c r="I17" s="5"/>
-      <x:c r="J17" s="5"/>
-      <x:c r="K17" s="5"/>
-      <x:c r="L17" s="5"/>
-      <x:c r="M17" s="5"/>
-      <x:c r="N17" s="5"/>
-      <x:c r="O17" s="5"/>
-      <x:c r="P17" s="5"/>
-      <x:c r="Q17" s="5"/>
-      <x:c r="R17" s="5"/>
-      <x:c r="S17" s="5"/>
-      <x:c r="T17" s="5"/>
-      <x:c r="U17" s="5"/>
-      <x:c r="V17" s="5"/>
-      <x:c r="W17" s="5"/>
-      <x:c r="X17" s="5"/>
+      <x:c r="B17" s="8"/>
+      <x:c r="C17" s="8"/>
+      <x:c r="D17" s="8"/>
+      <x:c r="E17" s="8"/>
+      <x:c r="F17" s="8"/>
+      <x:c r="G17" s="8"/>
+      <x:c r="H17" s="8"/>
+      <x:c r="I17" s="8"/>
+      <x:c r="J17" s="8"/>
+      <x:c r="K17" s="8"/>
+      <x:c r="L17" s="8"/>
+      <x:c r="M17" s="8"/>
+      <x:c r="N17" s="8"/>
+      <x:c r="O17" s="8"/>
+      <x:c r="P17" s="8"/>
+      <x:c r="Q17" s="8"/>
+      <x:c r="R17" s="8"/>
+      <x:c r="S17" s="8"/>
+      <x:c r="T17" s="8"/>
+      <x:c r="U17" s="8"/>
+      <x:c r="V17" s="8"/>
+      <x:c r="W17" s="8"/>
+      <x:c r="X17" s="8"/>
     </x:row>
     <x:row r="18" spans="1:24" ht="15" customHeight="1">
       <x:c r="A18" s="3" t="s">
@@ -766,13 +976,13 @@
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
     <x:oddHeader/>
     <x:oddFooter>&amp;C山田 太郎
-職務経歴書 ／ 作成日時（JST）：2026年10月29日 01:05&amp;R&amp;P / &amp;N</x:oddFooter>
+職務経歴書 ／ 作成日時（JST）：2026年10月29日 14:12&amp;R&amp;P / &amp;N</x:oddFooter>
     <x:evenHeader/>
     <x:evenFooter>&amp;C山田 太郎
-職務経歴書 ／ 作成日時（JST）：2026年10月29日 01:05&amp;R&amp;P / &amp;N</x:evenFooter>
+職務経歴書 ／ 作成日時（JST）：2026年10月29日 14:12&amp;R&amp;P / &amp;N</x:evenFooter>
     <x:firstHeader/>
     <x:firstFooter>&amp;C山田 太郎
-職務経歴書 ／ 作成日時（JST）：2026年10月29日 01:05&amp;R&amp;P / &amp;N</x:firstFooter>
+職務経歴書 ／ 作成日時（JST）：2026年10月29日 14:12&amp;R&amp;P / &amp;N</x:firstFooter>
   </x:headerFooter>
   <x:tableParts count="0"/>
 </x:worksheet>
@@ -808,165 +1018,605 @@
       </x:c>
     </x:row>
     <x:row r="5" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A5" s="3" t="s">
+      <x:c r="A5" s="9" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G5" s="3" t="s">
+      <x:c r="B5" s="10"/>
+      <x:c r="C5" s="10"/>
+      <x:c r="D5" s="10"/>
+      <x:c r="E5" s="10"/>
+      <x:c r="F5" s="11"/>
+      <x:c r="G5" s="9" t="s">
         <x:v>18</x:v>
       </x:c>
+      <x:c r="H5" s="10"/>
+      <x:c r="I5" s="10"/>
+      <x:c r="J5" s="10"/>
+      <x:c r="K5" s="10"/>
+      <x:c r="L5" s="10"/>
+      <x:c r="M5" s="10"/>
+      <x:c r="N5" s="10"/>
+      <x:c r="O5" s="10"/>
+      <x:c r="P5" s="10"/>
+      <x:c r="Q5" s="10"/>
+      <x:c r="R5" s="10"/>
+      <x:c r="S5" s="10"/>
+      <x:c r="T5" s="10"/>
+      <x:c r="U5" s="10"/>
+      <x:c r="V5" s="10"/>
+      <x:c r="W5" s="10"/>
+      <x:c r="X5" s="11"/>
     </x:row>
     <x:row r="6" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A6" s="3" t="s">
+      <x:c r="A6" s="4" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G6" s="3" t="s">
+      <x:c r="B6" s="5"/>
+      <x:c r="C6" s="5"/>
+      <x:c r="D6" s="5"/>
+      <x:c r="E6" s="5"/>
+      <x:c r="F6" s="6"/>
+      <x:c r="G6" s="4" t="s">
         <x:v>20</x:v>
       </x:c>
+      <x:c r="H6" s="5"/>
+      <x:c r="I6" s="5"/>
+      <x:c r="J6" s="5"/>
+      <x:c r="K6" s="5"/>
+      <x:c r="L6" s="5"/>
+      <x:c r="M6" s="5"/>
+      <x:c r="N6" s="5"/>
+      <x:c r="O6" s="5"/>
+      <x:c r="P6" s="5"/>
+      <x:c r="Q6" s="5"/>
+      <x:c r="R6" s="5"/>
+      <x:c r="S6" s="5"/>
+      <x:c r="T6" s="5"/>
+      <x:c r="U6" s="5"/>
+      <x:c r="V6" s="5"/>
+      <x:c r="W6" s="5"/>
+      <x:c r="X6" s="6"/>
     </x:row>
     <x:row r="7" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A7" s="3" t="s">
+      <x:c r="A7" s="4" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="G7" s="3" t="s">
+      <x:c r="B7" s="5"/>
+      <x:c r="C7" s="5"/>
+      <x:c r="D7" s="5"/>
+      <x:c r="E7" s="5"/>
+      <x:c r="F7" s="6"/>
+      <x:c r="G7" s="4" t="s">
         <x:v>22</x:v>
       </x:c>
+      <x:c r="H7" s="5"/>
+      <x:c r="I7" s="5"/>
+      <x:c r="J7" s="5"/>
+      <x:c r="K7" s="5"/>
+      <x:c r="L7" s="5"/>
+      <x:c r="M7" s="5"/>
+      <x:c r="N7" s="5"/>
+      <x:c r="O7" s="5"/>
+      <x:c r="P7" s="5"/>
+      <x:c r="Q7" s="5"/>
+      <x:c r="R7" s="5"/>
+      <x:c r="S7" s="5"/>
+      <x:c r="T7" s="5"/>
+      <x:c r="U7" s="5"/>
+      <x:c r="V7" s="5"/>
+      <x:c r="W7" s="5"/>
+      <x:c r="X7" s="6"/>
     </x:row>
     <x:row r="8" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A8" s="3" t="s">
+      <x:c r="A8" s="4" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="G8" s="3" t="s">
+      <x:c r="B8" s="5"/>
+      <x:c r="C8" s="5"/>
+      <x:c r="D8" s="5"/>
+      <x:c r="E8" s="5"/>
+      <x:c r="F8" s="6"/>
+      <x:c r="G8" s="4" t="s">
         <x:v>24</x:v>
       </x:c>
+      <x:c r="H8" s="5"/>
+      <x:c r="I8" s="5"/>
+      <x:c r="J8" s="5"/>
+      <x:c r="K8" s="5"/>
+      <x:c r="L8" s="5"/>
+      <x:c r="M8" s="5"/>
+      <x:c r="N8" s="5"/>
+      <x:c r="O8" s="5"/>
+      <x:c r="P8" s="5"/>
+      <x:c r="Q8" s="5"/>
+      <x:c r="R8" s="5"/>
+      <x:c r="S8" s="5"/>
+      <x:c r="T8" s="5"/>
+      <x:c r="U8" s="5"/>
+      <x:c r="V8" s="5"/>
+      <x:c r="W8" s="5"/>
+      <x:c r="X8" s="6"/>
     </x:row>
     <x:row r="9" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A9" s="3" t="s">
+      <x:c r="A9" s="4" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="G9" s="3" t="s">
+      <x:c r="B9" s="5"/>
+      <x:c r="C9" s="5"/>
+      <x:c r="D9" s="5"/>
+      <x:c r="E9" s="5"/>
+      <x:c r="F9" s="6"/>
+      <x:c r="G9" s="4" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="H9" s="5"/>
+      <x:c r="I9" s="5"/>
+      <x:c r="J9" s="5"/>
+      <x:c r="K9" s="5"/>
+      <x:c r="L9" s="5"/>
+      <x:c r="M9" s="5"/>
+      <x:c r="N9" s="5"/>
+      <x:c r="O9" s="5"/>
+      <x:c r="P9" s="5"/>
+      <x:c r="Q9" s="5"/>
+      <x:c r="R9" s="5"/>
+      <x:c r="S9" s="5"/>
+      <x:c r="T9" s="5"/>
+      <x:c r="U9" s="5"/>
+      <x:c r="V9" s="5"/>
+      <x:c r="W9" s="5"/>
+      <x:c r="X9" s="6"/>
     </x:row>
     <x:row r="10" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A10" s="3" t="s">
+      <x:c r="A10" s="4" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="G10" s="3" t="s">
+      <x:c r="B10" s="5"/>
+      <x:c r="C10" s="5"/>
+      <x:c r="D10" s="5"/>
+      <x:c r="E10" s="5"/>
+      <x:c r="F10" s="6"/>
+      <x:c r="G10" s="4" t="s">
         <x:v>28</x:v>
       </x:c>
+      <x:c r="H10" s="5"/>
+      <x:c r="I10" s="5"/>
+      <x:c r="J10" s="5"/>
+      <x:c r="K10" s="5"/>
+      <x:c r="L10" s="5"/>
+      <x:c r="M10" s="5"/>
+      <x:c r="N10" s="5"/>
+      <x:c r="O10" s="5"/>
+      <x:c r="P10" s="5"/>
+      <x:c r="Q10" s="5"/>
+      <x:c r="R10" s="5"/>
+      <x:c r="S10" s="5"/>
+      <x:c r="T10" s="5"/>
+      <x:c r="U10" s="5"/>
+      <x:c r="V10" s="5"/>
+      <x:c r="W10" s="5"/>
+      <x:c r="X10" s="6"/>
     </x:row>
     <x:row r="11" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A11" s="3" t="s">
+      <x:c r="A11" s="4" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="G11" s="3" t="s">
+      <x:c r="B11" s="5"/>
+      <x:c r="C11" s="5"/>
+      <x:c r="D11" s="5"/>
+      <x:c r="E11" s="5"/>
+      <x:c r="F11" s="6"/>
+      <x:c r="G11" s="4" t="s">
         <x:v>30</x:v>
       </x:c>
+      <x:c r="H11" s="5"/>
+      <x:c r="I11" s="5"/>
+      <x:c r="J11" s="5"/>
+      <x:c r="K11" s="5"/>
+      <x:c r="L11" s="5"/>
+      <x:c r="M11" s="5"/>
+      <x:c r="N11" s="5"/>
+      <x:c r="O11" s="5"/>
+      <x:c r="P11" s="5"/>
+      <x:c r="Q11" s="5"/>
+      <x:c r="R11" s="5"/>
+      <x:c r="S11" s="5"/>
+      <x:c r="T11" s="5"/>
+      <x:c r="U11" s="5"/>
+      <x:c r="V11" s="5"/>
+      <x:c r="W11" s="5"/>
+      <x:c r="X11" s="6"/>
     </x:row>
     <x:row r="12" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A12" s="3" t="s">
+      <x:c r="A12" s="4" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="G12" s="3" t="s">
+      <x:c r="B12" s="5"/>
+      <x:c r="C12" s="5"/>
+      <x:c r="D12" s="5"/>
+      <x:c r="E12" s="5"/>
+      <x:c r="F12" s="6"/>
+      <x:c r="G12" s="4" t="s">
         <x:v>32</x:v>
       </x:c>
+      <x:c r="H12" s="5"/>
+      <x:c r="I12" s="5"/>
+      <x:c r="J12" s="5"/>
+      <x:c r="K12" s="5"/>
+      <x:c r="L12" s="5"/>
+      <x:c r="M12" s="5"/>
+      <x:c r="N12" s="5"/>
+      <x:c r="O12" s="5"/>
+      <x:c r="P12" s="5"/>
+      <x:c r="Q12" s="5"/>
+      <x:c r="R12" s="5"/>
+      <x:c r="S12" s="5"/>
+      <x:c r="T12" s="5"/>
+      <x:c r="U12" s="5"/>
+      <x:c r="V12" s="5"/>
+      <x:c r="W12" s="5"/>
+      <x:c r="X12" s="6"/>
     </x:row>
     <x:row r="13" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A13" s="3" t="s">
+      <x:c r="A13" s="4" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="G13" s="3" t="s">
+      <x:c r="B13" s="5"/>
+      <x:c r="C13" s="5"/>
+      <x:c r="D13" s="5"/>
+      <x:c r="E13" s="5"/>
+      <x:c r="F13" s="6"/>
+      <x:c r="G13" s="4" t="s">
         <x:v>34</x:v>
       </x:c>
+      <x:c r="H13" s="5"/>
+      <x:c r="I13" s="5"/>
+      <x:c r="J13" s="5"/>
+      <x:c r="K13" s="5"/>
+      <x:c r="L13" s="5"/>
+      <x:c r="M13" s="5"/>
+      <x:c r="N13" s="5"/>
+      <x:c r="O13" s="5"/>
+      <x:c r="P13" s="5"/>
+      <x:c r="Q13" s="5"/>
+      <x:c r="R13" s="5"/>
+      <x:c r="S13" s="5"/>
+      <x:c r="T13" s="5"/>
+      <x:c r="U13" s="5"/>
+      <x:c r="V13" s="5"/>
+      <x:c r="W13" s="5"/>
+      <x:c r="X13" s="6"/>
     </x:row>
     <x:row r="14" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A14" s="3" t="s">
+      <x:c r="A14" s="4" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="G14" s="3" t="s">
+      <x:c r="B14" s="5"/>
+      <x:c r="C14" s="5"/>
+      <x:c r="D14" s="5"/>
+      <x:c r="E14" s="5"/>
+      <x:c r="F14" s="6"/>
+      <x:c r="G14" s="4" t="s">
         <x:v>36</x:v>
       </x:c>
+      <x:c r="H14" s="5"/>
+      <x:c r="I14" s="5"/>
+      <x:c r="J14" s="5"/>
+      <x:c r="K14" s="5"/>
+      <x:c r="L14" s="5"/>
+      <x:c r="M14" s="5"/>
+      <x:c r="N14" s="5"/>
+      <x:c r="O14" s="5"/>
+      <x:c r="P14" s="5"/>
+      <x:c r="Q14" s="5"/>
+      <x:c r="R14" s="5"/>
+      <x:c r="S14" s="5"/>
+      <x:c r="T14" s="5"/>
+      <x:c r="U14" s="5"/>
+      <x:c r="V14" s="5"/>
+      <x:c r="W14" s="5"/>
+      <x:c r="X14" s="6"/>
     </x:row>
     <x:row r="15" spans="1:24" ht="15" customHeight="1"/>
     <x:row r="16" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A16" s="3" t="s">
+      <x:c r="A16" s="9" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G16" s="3" t="s">
+      <x:c r="B16" s="10"/>
+      <x:c r="C16" s="10"/>
+      <x:c r="D16" s="10"/>
+      <x:c r="E16" s="10"/>
+      <x:c r="F16" s="11"/>
+      <x:c r="G16" s="9" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="H16" s="10"/>
+      <x:c r="I16" s="10"/>
+      <x:c r="J16" s="10"/>
+      <x:c r="K16" s="10"/>
+      <x:c r="L16" s="10"/>
+      <x:c r="M16" s="10"/>
+      <x:c r="N16" s="10"/>
+      <x:c r="O16" s="10"/>
+      <x:c r="P16" s="10"/>
+      <x:c r="Q16" s="10"/>
+      <x:c r="R16" s="10"/>
+      <x:c r="S16" s="10"/>
+      <x:c r="T16" s="10"/>
+      <x:c r="U16" s="10"/>
+      <x:c r="V16" s="10"/>
+      <x:c r="W16" s="10"/>
+      <x:c r="X16" s="11"/>
     </x:row>
     <x:row r="17" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A17" s="3" t="s">
+      <x:c r="A17" s="4" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G17" s="3" t="s">
+      <x:c r="B17" s="5"/>
+      <x:c r="C17" s="5"/>
+      <x:c r="D17" s="5"/>
+      <x:c r="E17" s="5"/>
+      <x:c r="F17" s="6"/>
+      <x:c r="G17" s="4" t="s">
         <x:v>38</x:v>
       </x:c>
+      <x:c r="H17" s="5"/>
+      <x:c r="I17" s="5"/>
+      <x:c r="J17" s="5"/>
+      <x:c r="K17" s="5"/>
+      <x:c r="L17" s="5"/>
+      <x:c r="M17" s="5"/>
+      <x:c r="N17" s="5"/>
+      <x:c r="O17" s="5"/>
+      <x:c r="P17" s="5"/>
+      <x:c r="Q17" s="5"/>
+      <x:c r="R17" s="5"/>
+      <x:c r="S17" s="5"/>
+      <x:c r="T17" s="5"/>
+      <x:c r="U17" s="5"/>
+      <x:c r="V17" s="5"/>
+      <x:c r="W17" s="5"/>
+      <x:c r="X17" s="6"/>
     </x:row>
     <x:row r="18" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A18" s="3" t="s">
+      <x:c r="A18" s="4" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="G18" s="3" t="s">
+      <x:c r="B18" s="5"/>
+      <x:c r="C18" s="5"/>
+      <x:c r="D18" s="5"/>
+      <x:c r="E18" s="5"/>
+      <x:c r="F18" s="6"/>
+      <x:c r="G18" s="4" t="s">
         <x:v>22</x:v>
       </x:c>
+      <x:c r="H18" s="5"/>
+      <x:c r="I18" s="5"/>
+      <x:c r="J18" s="5"/>
+      <x:c r="K18" s="5"/>
+      <x:c r="L18" s="5"/>
+      <x:c r="M18" s="5"/>
+      <x:c r="N18" s="5"/>
+      <x:c r="O18" s="5"/>
+      <x:c r="P18" s="5"/>
+      <x:c r="Q18" s="5"/>
+      <x:c r="R18" s="5"/>
+      <x:c r="S18" s="5"/>
+      <x:c r="T18" s="5"/>
+      <x:c r="U18" s="5"/>
+      <x:c r="V18" s="5"/>
+      <x:c r="W18" s="5"/>
+      <x:c r="X18" s="6"/>
     </x:row>
     <x:row r="19" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A19" s="3" t="s">
+      <x:c r="A19" s="4" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="G19" s="3" t="s">
+      <x:c r="B19" s="5"/>
+      <x:c r="C19" s="5"/>
+      <x:c r="D19" s="5"/>
+      <x:c r="E19" s="5"/>
+      <x:c r="F19" s="6"/>
+      <x:c r="G19" s="4" t="s">
         <x:v>39</x:v>
       </x:c>
+      <x:c r="H19" s="5"/>
+      <x:c r="I19" s="5"/>
+      <x:c r="J19" s="5"/>
+      <x:c r="K19" s="5"/>
+      <x:c r="L19" s="5"/>
+      <x:c r="M19" s="5"/>
+      <x:c r="N19" s="5"/>
+      <x:c r="O19" s="5"/>
+      <x:c r="P19" s="5"/>
+      <x:c r="Q19" s="5"/>
+      <x:c r="R19" s="5"/>
+      <x:c r="S19" s="5"/>
+      <x:c r="T19" s="5"/>
+      <x:c r="U19" s="5"/>
+      <x:c r="V19" s="5"/>
+      <x:c r="W19" s="5"/>
+      <x:c r="X19" s="6"/>
     </x:row>
     <x:row r="20" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A20" s="3" t="s">
+      <x:c r="A20" s="4" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="G20" s="3" t="s">
+      <x:c r="B20" s="5"/>
+      <x:c r="C20" s="5"/>
+      <x:c r="D20" s="5"/>
+      <x:c r="E20" s="5"/>
+      <x:c r="F20" s="6"/>
+      <x:c r="G20" s="4" t="s">
         <x:v>40</x:v>
       </x:c>
+      <x:c r="H20" s="5"/>
+      <x:c r="I20" s="5"/>
+      <x:c r="J20" s="5"/>
+      <x:c r="K20" s="5"/>
+      <x:c r="L20" s="5"/>
+      <x:c r="M20" s="5"/>
+      <x:c r="N20" s="5"/>
+      <x:c r="O20" s="5"/>
+      <x:c r="P20" s="5"/>
+      <x:c r="Q20" s="5"/>
+      <x:c r="R20" s="5"/>
+      <x:c r="S20" s="5"/>
+      <x:c r="T20" s="5"/>
+      <x:c r="U20" s="5"/>
+      <x:c r="V20" s="5"/>
+      <x:c r="W20" s="5"/>
+      <x:c r="X20" s="6"/>
     </x:row>
     <x:row r="21" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A21" s="3" t="s">
+      <x:c r="A21" s="4" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="G21" s="3" t="s">
+      <x:c r="B21" s="5"/>
+      <x:c r="C21" s="5"/>
+      <x:c r="D21" s="5"/>
+      <x:c r="E21" s="5"/>
+      <x:c r="F21" s="6"/>
+      <x:c r="G21" s="4" t="s">
         <x:v>41</x:v>
       </x:c>
+      <x:c r="H21" s="5"/>
+      <x:c r="I21" s="5"/>
+      <x:c r="J21" s="5"/>
+      <x:c r="K21" s="5"/>
+      <x:c r="L21" s="5"/>
+      <x:c r="M21" s="5"/>
+      <x:c r="N21" s="5"/>
+      <x:c r="O21" s="5"/>
+      <x:c r="P21" s="5"/>
+      <x:c r="Q21" s="5"/>
+      <x:c r="R21" s="5"/>
+      <x:c r="S21" s="5"/>
+      <x:c r="T21" s="5"/>
+      <x:c r="U21" s="5"/>
+      <x:c r="V21" s="5"/>
+      <x:c r="W21" s="5"/>
+      <x:c r="X21" s="6"/>
     </x:row>
     <x:row r="22" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A22" s="3" t="s">
+      <x:c r="A22" s="4" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="G22" s="3" t="s">
+      <x:c r="B22" s="5"/>
+      <x:c r="C22" s="5"/>
+      <x:c r="D22" s="5"/>
+      <x:c r="E22" s="5"/>
+      <x:c r="F22" s="6"/>
+      <x:c r="G22" s="4" t="s">
         <x:v>42</x:v>
       </x:c>
+      <x:c r="H22" s="5"/>
+      <x:c r="I22" s="5"/>
+      <x:c r="J22" s="5"/>
+      <x:c r="K22" s="5"/>
+      <x:c r="L22" s="5"/>
+      <x:c r="M22" s="5"/>
+      <x:c r="N22" s="5"/>
+      <x:c r="O22" s="5"/>
+      <x:c r="P22" s="5"/>
+      <x:c r="Q22" s="5"/>
+      <x:c r="R22" s="5"/>
+      <x:c r="S22" s="5"/>
+      <x:c r="T22" s="5"/>
+      <x:c r="U22" s="5"/>
+      <x:c r="V22" s="5"/>
+      <x:c r="W22" s="5"/>
+      <x:c r="X22" s="6"/>
     </x:row>
     <x:row r="23" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A23" s="3" t="s">
+      <x:c r="A23" s="4" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="G23" s="3" t="s">
+      <x:c r="B23" s="5"/>
+      <x:c r="C23" s="5"/>
+      <x:c r="D23" s="5"/>
+      <x:c r="E23" s="5"/>
+      <x:c r="F23" s="6"/>
+      <x:c r="G23" s="4" t="s">
         <x:v>43</x:v>
       </x:c>
+      <x:c r="H23" s="5"/>
+      <x:c r="I23" s="5"/>
+      <x:c r="J23" s="5"/>
+      <x:c r="K23" s="5"/>
+      <x:c r="L23" s="5"/>
+      <x:c r="M23" s="5"/>
+      <x:c r="N23" s="5"/>
+      <x:c r="O23" s="5"/>
+      <x:c r="P23" s="5"/>
+      <x:c r="Q23" s="5"/>
+      <x:c r="R23" s="5"/>
+      <x:c r="S23" s="5"/>
+      <x:c r="T23" s="5"/>
+      <x:c r="U23" s="5"/>
+      <x:c r="V23" s="5"/>
+      <x:c r="W23" s="5"/>
+      <x:c r="X23" s="6"/>
     </x:row>
     <x:row r="24" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A24" s="3" t="s">
+      <x:c r="A24" s="4" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="G24" s="3" t="s">
+      <x:c r="B24" s="5"/>
+      <x:c r="C24" s="5"/>
+      <x:c r="D24" s="5"/>
+      <x:c r="E24" s="5"/>
+      <x:c r="F24" s="6"/>
+      <x:c r="G24" s="4" t="s">
         <x:v>44</x:v>
       </x:c>
+      <x:c r="H24" s="5"/>
+      <x:c r="I24" s="5"/>
+      <x:c r="J24" s="5"/>
+      <x:c r="K24" s="5"/>
+      <x:c r="L24" s="5"/>
+      <x:c r="M24" s="5"/>
+      <x:c r="N24" s="5"/>
+      <x:c r="O24" s="5"/>
+      <x:c r="P24" s="5"/>
+      <x:c r="Q24" s="5"/>
+      <x:c r="R24" s="5"/>
+      <x:c r="S24" s="5"/>
+      <x:c r="T24" s="5"/>
+      <x:c r="U24" s="5"/>
+      <x:c r="V24" s="5"/>
+      <x:c r="W24" s="5"/>
+      <x:c r="X24" s="6"/>
     </x:row>
     <x:row r="25" spans="1:24" ht="15" customHeight="1">
-      <x:c r="A25" s="3" t="s">
+      <x:c r="A25" s="4" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="G25" s="3" t="s">
+      <x:c r="B25" s="5"/>
+      <x:c r="C25" s="5"/>
+      <x:c r="D25" s="5"/>
+      <x:c r="E25" s="5"/>
+      <x:c r="F25" s="6"/>
+      <x:c r="G25" s="4" t="s">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="H25" s="5"/>
+      <x:c r="I25" s="5"/>
+      <x:c r="J25" s="5"/>
+      <x:c r="K25" s="5"/>
+      <x:c r="L25" s="5"/>
+      <x:c r="M25" s="5"/>
+      <x:c r="N25" s="5"/>
+      <x:c r="O25" s="5"/>
+      <x:c r="P25" s="5"/>
+      <x:c r="Q25" s="5"/>
+      <x:c r="R25" s="5"/>
+      <x:c r="S25" s="5"/>
+      <x:c r="T25" s="5"/>
+      <x:c r="U25" s="5"/>
+      <x:c r="V25" s="5"/>
+      <x:c r="W25" s="5"/>
+      <x:c r="X25" s="6"/>
     </x:row>
     <x:row r="26" ht="15" customHeight="1"/>
   </x:sheetData>
@@ -1021,13 +1671,13 @@
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
     <x:oddHeader/>
     <x:oddFooter>&amp;C山田 太郎
-案件経歴 ／ 作成日時（JST）：2026年10月29日 01:05&amp;R&amp;P / &amp;N</x:oddFooter>
+案件経歴 ／ 作成日時（JST）：2026年10月29日 14:12&amp;R&amp;P / &amp;N</x:oddFooter>
     <x:evenHeader/>
     <x:evenFooter>&amp;C山田 太郎
-案件経歴 ／ 作成日時（JST）：2026年10月29日 01:05&amp;R&amp;P / &amp;N</x:evenFooter>
+案件経歴 ／ 作成日時（JST）：2026年10月29日 14:12&amp;R&amp;P / &amp;N</x:evenFooter>
     <x:firstHeader/>
     <x:firstFooter>&amp;C山田 太郎
-案件経歴 ／ 作成日時（JST）：2026年10月29日 01:05&amp;R&amp;P / &amp;N</x:firstFooter>
+案件経歴 ／ 作成日時（JST）：2026年10月29日 14:12&amp;R&amp;P / &amp;N</x:firstFooter>
   </x:headerFooter>
   <x:tableParts count="0"/>
 </x:worksheet>
